--- a/results/run_1/metrics_benchmark_rc.xlsx
+++ b/results/run_1/metrics_benchmark_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,11 +486,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Train Time (s)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>comment</t>
         </is>
       </c>
@@ -502,41 +497,80 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1032112804944665</v>
+        <v>0.001855810355352211</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3212651249271644</v>
+        <v>0.04307911739291105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.293421082839479</v>
+        <v>0.01795608702838828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7856229770131442</v>
+        <v>0.3203747300000011</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2925793702461091</v>
+        <v>-0.00034129841346154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8008530208785685</v>
+        <v>0.9963948217263092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.410323091839259</v>
+        <v>0.1891187568251931</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01760859260085675</v>
+        <v>0.00185569387074518</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1326973722454848</v>
+        <v>0.04307776538709013</v>
       </c>
       <c r="K2" t="n">
-        <v>1.937163798433682e-05</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0819668999993155</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>RC basé IDF, sans airgap</t>
+        <v>3.498224249266557e-05</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.001855810355352211</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04307911739291105</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01795608702838828</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3203747300000011</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.00034129841346154</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9963948217263092</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1891187568251931</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.00185569387074518</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.04307776538709013</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.498224249266557e-05</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
         </is>
       </c>
     </row>

--- a/results/run_1/metrics_benchmark_rc.xlsx
+++ b/results/run_1/metrics_benchmark_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,48 @@
         <v>3.498224249266557e-05</v>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.001855810355352211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.04307911739291105</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01795608702838828</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3203747300000011</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.00034129841346154</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9963948217263092</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1891187568251931</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.00185569387074518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.04307776538709013</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.332149499511038e-05</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>benchmark, step 15min, 1jour/4</t>
         </is>
